--- a/design/ip_common_lib/clk_gate/caselist.xlsx
+++ b/design/ip_common_lib/clk_gate/caselist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learn\IC\project\SOC\design\ip_common_lib\clk_gate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC5467E-8A97-4C23-886F-E903D1FB78FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D07448-11F1-430F-85A9-5ACDDB7D97CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3300" yWindow="1635" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -507,15 +507,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.4140625" customWidth="1"/>
-    <col min="2" max="2" width="10.58203125" customWidth="1"/>
-    <col min="3" max="3" width="15.08203125" customWidth="1"/>
-    <col min="4" max="4" width="29.83203125" customWidth="1"/>
+    <col min="1" max="1" width="21.375" customWidth="1"/>
+    <col min="2" max="2" width="10.625" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="29.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -532,7 +532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -549,7 +549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1">
         <v>2</v>
       </c>
@@ -563,7 +563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>3</v>
       </c>
@@ -577,7 +577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>4</v>
       </c>
@@ -591,7 +591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>5</v>
       </c>
@@ -605,7 +605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>6</v>
       </c>
@@ -619,7 +619,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -636,7 +636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>8</v>
       </c>
@@ -650,7 +650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
@@ -667,7 +667,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3">
         <v>10</v>
       </c>
@@ -681,7 +681,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3">
         <v>11</v>
       </c>
@@ -692,7 +692,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3">
         <v>12</v>
       </c>
@@ -703,7 +703,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C14" t="s">
         <v>32</v>
       </c>
